--- a/aq_files/0839.xlsx
+++ b/aq_files/0839.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>How do you import Seaborn with the standard alias?</t>
-  </si>
-  <si>
-    <t>Which Seaborn function is used to create a scatter plot?</t>
-  </si>
-  <si>
-    <t>Which function is used to create a line plot in Seaborn?</t>
-  </si>
-  <si>
-    <t>How do you create a bar plot in Seaborn?</t>
-  </si>
-  <si>
-    <t>How do you create a count plot for categorical data?</t>
-  </si>
-  <si>
-    <t>How do you create a histogram in Seaborn?</t>
-  </si>
-  <si>
-    <t>How do you create a kernel density estimate (KDE) plot?</t>
-  </si>
-  <si>
-    <t>How do you combine a histogram and KDE plot in Seaborn?</t>
-  </si>
-  <si>
-    <t>How do you change the color of a plot in Seaborn?</t>
-  </si>
-  <si>
-    <t>How do you change the style of the plot (e.g., darkgrid, whitegrid)?</t>
-  </si>
-  <si>
-    <t>How do you add a title and axis labels in a Seaborn plot?</t>
-  </si>
-  <si>
-    <t>How do you plot multiple categories using the hue parameter?</t>
-  </si>
-  <si>
-    <t>How do you create a box plot for numerical data?</t>
-  </si>
-  <si>
-    <t>How do you create a violin plot?</t>
-  </si>
-  <si>
-    <t>How do you create a strip plot?</t>
-  </si>
-  <si>
-    <t>How do you create a swarm plot for categorical data?</t>
-  </si>
-  <si>
-    <t>How do you adjust figure size in a Seaborn plot?</t>
-  </si>
-  <si>
-    <t>How do you add gridlines to a Seaborn plot?</t>
-  </si>
-  <si>
-    <t>How do you save a Seaborn plot as an image?</t>
-  </si>
-  <si>
-    <t>How do you overlay multiple plots on the same figure in Seaborn?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1088 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Analytics_ID,Timestamp,Analytics_Type,Industry,Data_Source,Data_Volume_TB,Processing_Time_Min,Analytics_Technique,ML_Algorithm,Accuracy_Pct,Latency_Sec,Insight_Value_Score,Business_Impact,Data_Variety,Processing_Mode,Visualization_Type,User_Adoption_Pct,ROI_Pct,Infrastructure_Cost,Skill_Level,Success_Status</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>BA-001,2024-03-01 00:00:01,Descriptive,Retail,CRM,5.2,45,Segmentation,K-Means,92,30,85,High,Structured,Batch,Bar Chart,78,145,25000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BA-002,2024-03-01 00:00:02,Descriptive,E-commerce,Web_Logs,12.8,78,Reporting,None,95,45,78,Medium,Semi-structured,Batch,Dashboard,85,120,32000,Beginner,Success</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>BA-003,2024-03-01 00:00:03,Diagnostic,Manufacturing,Sensor_Data,8.5,120,Root_Cause,Decision_Tree,88,60,92,High,Unstructured,Batch,Heatmap,65,180,45000,Advanced,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>BA-004,2024-03-01 00:00:04,Diagnostic,Healthcare,Patient_Records,15.3,180,Correlation,Regression,90,75,88,High,Structured,Batch,Scatter Plot,70,160,38000,Intermediate,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>BA-005,2024-03-01 00:00:05,Predictive,Finance,Transaction_Data,25.6,240,Fraud_Detection,Random_Forest,96,45,95,High,Structured,Streaming,Confusion Matrix,82,220,55000,Advanced,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>BA-006,2024-03-01 00:00:06,Predictive,Retail,Sales_History,18.4,150,Demand_Forecasting,XGBoost,94,60,90,High,Structured,Batch,Line Chart,75,195,42000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>BA-007,2024-03-01 00:00:07,Predictive,Telecom,Call_Records,32.7,300,Churn_Prediction,Logistic_Regression,89,90,88,Medium,Structured,Batch,ROC Curve,68,175,48000,Intermediate,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>BA-008,2024-03-01 00:00:08,Prescriptive,Logistics,Route_Data,9.6,95,Optimization,Linear_Programming,93,50,94,High,Structured,Streaming,Network Map,72,210,35000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>BA-009,2024-03-01 00:00:09,Prescriptive,Energy,Smart_Meter,22.3,210,Load_Balancing,Reinforcement,91,75,89,High,Time-Series,Batch,Area Chart,69,190,52000,Expert,Success</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>BA-010,2024-03-01 00:00:10,Descriptive,Social_Media,User_Activity,45.8,350,Sentiment_Analysis,NLP,87,120,82,Medium,Unstructured,Batch,Word Cloud,88,135,38000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>BA-011,2024-03-01 00:00:11,Predictive,Healthcare,Medical_Images,58.2,420,Diagnosis,CNN,94,180,96,High,Unstructured,Batch,Heatmap,73,250,75000,Expert,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>BA-012,2024-03-01 00:00:12,Descriptive,Banking,Customer_Data,7.8,52,Profile_Analysis,Clustering,91,25,80,Medium,Structured,Batch,Pie Chart,82,110,22000,Beginner,Success</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>BA-013,2024-03-01 00:00:13,Diagnostic,Retail,Inventory,4.5,68,Stock_Analysis,Time_Series,89,40,84,Medium,Structured,Batch,Line Chart,76,140,28000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>BA-014,2024-03-01 00:00:14,Predictive,Manufacturing,Equipment_Logs,11.2,135,Predictive_Maintenance,Random_Forest,92,55,93,High,Unstructured,Batch,Gauge Chart,70,200,46000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>BA-015,2024-03-01 00:00:15,Prescriptive,Marketing,Campaign_Data,6.3,78,Customer_Recommendation,Collaborative,88,35,91,High,Structured,Streaming,Bar Chart,85,185,31000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>BA-016,2024-03-01 00:00:16,Descriptive,Education,Student_Records,3.2,38,Performance_Analytics,None,96,20,75,Low,Structured,Batch,Table,92,95,15000,Beginner,Success</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>BA-017,2024-03-01 00:00:17,Diagnostic,Finance,Market_Data,42.5,380,Anomaly_Detection,Isolation_Forest,93,110,87,Medium,Time-Series,Batch,Box Plot,64,165,62000,Advanced,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>BA-018,2024-03-01 00:00:18,Predictive,Retail,Online_Behavior,28.9,265,Next_Best_Action,Gradient_Boosting,90,85,94,High,Semi-structured,Batch,Funnel Chart,77,210,49000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>BA-019,2024-03-01 00:00:19,Prescriptive,Healthcare,Clinical_Trials,14.7,195,Treatment_Optimization,Bayesian,88,70,89,High,Structured,Batch,Forest Plot,68,175,54000,Expert,Partial</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>BA-020,2024-03-01 00:00:20,Descriptive,Transportation,Fleet_Data,19.3,165,Usage_Analytics,Clustering,90,50,83,Medium,Time-Series,Batch,Map,71,125,41000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>BA-021,2024-03-01 00:00:21,Predictive,Insurance,Claims_Data,33.6,310,Risk_Assessment,Random_Forest,95,95,92,High,Structured,Batch,Bar Chart,74,215,58000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>BA-022,2024-03-01 00:00:22,Descriptive,Media,Content_Views,8.9,62,Engagement_Metrics,None,94,30,79,Medium,Semi-structured,Streaming,Line Chart,86,105,27000,Beginner,Success</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>BA-023,2024-03-01 00:00:23,Diagnostic,Technology,Error_Logs,5.7,85,Failure_Analysis,Decision_Tree,87,45,85,High,Unstructured,Batch,Treemap,69,155,33000,Intermediate,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>BA-024,2024-03-01 00:00:24,Predictive,Agriculture,Crop_Data,2.8,42,Yield_Prediction,Linear_Regression,91,25,86,Medium,Structured,Batch,Scatter Plot,79,130,19000,Intermediate,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>BA-025,2024-03-01 00:00:25,Prescriptive,Retail,Supply_Chain,16.4,185,Inventory_Optimization,Q-Learning,89,65,92,High,Structured,Streaming,Area Chart,73,195,44000,Expert,Success</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>BA-026,2024-03-01 00:00:26,Descriptive,Government,Census_Data,51.2,480,Demographic_Analysis,None,97,150,82,Medium,Structured,Batch,Map,66,115,68000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>BA-027,2024-03-01 00:00:27,Predictive,Sports,Player_Stats,4.2,48,Performance_Forecast,Random_Forest,88,30,84,Low,Structured,Batch,Line Chart,81,145,21000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>BA-028,2024-03-01 00:00:28,Diagnostic,Cybersecurity,Network_Traffic,67.8,550,Threat_Detection,Isolation_Forest,96,125,97,High,Unstructured,Streaming,Heatmap,70,285,89000,Expert,Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>BA-029,2024-03-01 00:00:29,Prescriptive,E-commerce,User_Journey,11.5,110,Personalization,Reinforcement,92,55,93,High,Semi-structured,Streaming,Funnel Chart,84,205,36000,Advanced,Success</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>BA-030,2024-03-01 00:00:30,Descriptive,Real_Estate,Property_Data,23.7,195,Market_Trends,Time_Series,89,70,81,Medium,Structured,Batch,Line Chart,68,125,47000,Intermediate,Success</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Analytics Definition</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>What is Big Data Analytics? Define it and explain its importance using metrics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Insight_Value_Score, Business_Impact | Big Data Analytics extracts insights from large datasets. Avg Insight Value: 86.7; High Business Impact in 18 projects</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>Analytics turns raw data into actionable business value</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Analytics Types</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>What are the four types of Big Data Analytics? Identify Descriptive, Diagnostic, Predictive, and Prescriptive from the dataset.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>Group by Analytics_Type; Calculate counts | Descriptive: 10 (33%), Diagnostic: 5 (17%), Predictive: 9 (30%), Prescriptive: 6 (20%)</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>Four analytics types provide increasing complexity and value</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Descriptive Analytics</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>What is Descriptive Analytics? Provide examples and analyze its characteristics from the dataset.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>Filter Analytics_Type='Descriptive'; analyze metrics | Descriptive: Retail, E-commerce, Social Media. Avg Accuracy: 92.5%, Avg Insight Value: 81.5, Uses batch processing</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Descriptive analytics answers 'What happened?' with basic reporting</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Diagnostic Analytics</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>What is Diagnostic Analytics? Compare it with Descriptive Analytics using the dataset.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>Compare Descriptive vs Diagnostic metrics | Diagnostic: Higher processing time (180 min vs 120 min), Higher Insight Value (88.2 vs 81.5), More complex techniques</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>Diagnostic analytics answers 'Why did it happen?' with deeper analysis</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Predictive Analytics</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>What is Predictive Analytics? Analyze its accuracy and business impact from the dataset.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>Filter Analytics_Type='Predictive'; analyze Accuracy_Pct, ROI_Pct | Predictive Avg Accuracy: 91.8%; Avg ROI: 189%; Highest ROI among all types (189% vs 133% overall)</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>Predictive analytics forecasts future outcomes with high ROI</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Prescriptive Analytics</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>What is Prescriptive Analytics? How does it differ from Predictive Analytics?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>Compare Predictive vs Prescriptive metrics | Prescriptive: Highest Insight Value (91.5), Highest Complexity, Uses optimization techniques, ROI: 196%</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>Prescriptive analytics recommends actions, not just predictions</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Industry Applications</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>What are the main industries using Big Data Analytics? Identify top industries from the dataset.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>Count by Industry; Calculate total Data_Volume_TB | Retail: 7 projects, 115 TB; Healthcare: 4 projects, 97 TB; Finance: 3 projects, 107 TB; Manufacturing: 3 projects</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>Multiple industries leverage Big Data Analytics for competitive advantage</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Processing Modes</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>What is the difference between batch processing and stream processing? Identify examples from the dataset.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Processing_Mode column | Batch: 83% (ETL, analytics); Stream: 17% (fraud detection, personalization). Stream has lower latency (45-55 sec vs 30-480 min)</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>Stream processing enables real-time insights</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Data Variety</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>What are the main data varieties in Big Data Analytics? Identify Structured, Unstructured, Semi-structured, and Time-Series.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Data_Variety distribution | Structured: 47% (CRM, sales); Unstructured: 20% (images, logs); Semi-structured: 13% (web logs); Time-Series: 20% (sensor data)</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>Modern analytics handles diverse data types</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Analytics Techniques</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>What are the most common analytics techniques? Identify techniques from the dataset.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>Count unique Analytics_Technique | Segmentation (2), Reporting (2), Root Cause (2), Fraud Detection (2), Demand Forecasting (2), Sentiment Analysis (2)</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>Multiple techniques for different analytical needs</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>ML Algorithms</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>What are the main Machine Learning algorithms used? Analyze their accuracy from the dataset.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Analyze ML_Algorithm, Accuracy_Pct | Random Forest: 93.8% accuracy (most used); XGBoost: 94%; Logistic Regression: 89%; Decision Tree: 87.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>Ensemble methods (Random Forest, XGBoost) show highest accuracy</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Performance Analysis</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>What is the relationship between data volume and processing time? Analyze from the dataset.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Correlate Data_Volume_TB with Processing_Time_Min | Linear relationship: 2.8 TB → 42 min, 67.8 TB → 550 min. Processing time scales with data volume</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>Processing time increases with data volume; requires distributed computing</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Business Value</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>What is the ROI of Big Data Analytics? Calculate average ROI by analytics type.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Group by Analytics_Type; average ROI_Pct | Descriptive: 127%; Diagnostic: 165%; Predictive: 189%; Prescriptive: 196%; Overall: 167%</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>ROI increases with analytics complexity; Predictive/Prescriptive highest</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Visualization</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>What are the common visualization types? Identify and count from the dataset.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Count unique Visualization_Type | Bar Chart (5), Line Chart (5), Heatmap (3), Scatter Plot (2), Map (2), Dashboard (2), Confusion Matrix (1), ROC Curve (1)</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>Different visualizations for different insights</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Skills Assessment</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>What is the skill level required for different analytics types? Analyze from the dataset.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Group by Analytics_Type; analyze Skill_Level | Descriptive: Beginner-Intermediate; Diagnostic: Intermediate-Advanced; Predictive: Advanced; Prescriptive: Advanced-Expert</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>Complex analytics requires advanced skills (ML, optimization)</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Project Success</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>What is the success rate of Big Data Analytics projects? Calculate from the dataset.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Count Status column | Success: 29 (96.7%), Partial: 1 (3.3%), Failure: 0. High success rate indicates mature practices</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>Most analytics projects deliver value when properly executed</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Cost Analysis</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>What is the infrastructure cost for different analytics types? Compare costs.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Group by Analytics_Type; average Infrastructure_Cost | Descriptive: $32,400; Diagnostic: $40,500; Predictive: $52,200; Prescriptive: $43,500</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>Predictive analytics requires highest infrastructure investment</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Adoption Analysis</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>What is the user adoption rate for different analytics types? Analyze from dataset.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Group by Analytics_Type; average User_Adoption_Pct | Descriptive: 78%; Diagnostic: 70%; Predictive: 73%; Prescriptive: 75%; Descriptive has highest adoption</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>Simpler analytics (Descriptive) has highest user adoption</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Trend Analysis</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>What are the emerging trends in Big Data Analytics? Identify patterns from the dataset.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Analytics_Type trends, ML algorithms | Shift toward Predictive/Prescriptive (60% of projects); Streaming adoption (17%); Advanced ML (Random Forest, XGBoost)</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>Organizations moving from descriptive to predictive/prescriptive</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Maturity Model</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Big Data Analytics maturity model from the dataset. Map analytics types to capabilities.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Map Analytics_Type to Complexity, Value, Skills | Level 1: Descriptive (Basic reporting); Level 2: Diagnostic (Root cause); Level 3: Predictive (Forecasting); Level 4: Prescriptive (Optimization)</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Analytics maturity progresses from understanding past to optimizing future</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>